--- a/data/seed/2026-08/export_20260831_0559.xlsx
+++ b/data/seed/2026-08/export_20260831_0559.xlsx
@@ -38,7 +38,7 @@
     <t>Branch</t>
   </si>
   <si>
-    <t>AIBL-2026-149221</t>
+    <t>AIBL-2026-202017</t>
   </si>
   <si>
     <t>New Business</t>
@@ -50,316 +50,334 @@
     <t>Completed - STP</t>
   </si>
   <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>AIBL-2026-930207</t>
+  </si>
+  <si>
+    <t>Policy Issuance - Single Premium</t>
+  </si>
+  <si>
+    <t>AIBL-2026-471158</t>
+  </si>
+  <si>
     <t>Dublin</t>
   </si>
   <si>
-    <t>AIBL-2026-658571</t>
+    <t>AIBL-2026-224307</t>
   </si>
   <si>
     <t>Policy Issuance</t>
   </si>
   <si>
+    <t>Limerick</t>
+  </si>
+  <si>
+    <t>AIBL-2026-775678</t>
+  </si>
+  <si>
+    <t>Underwriting</t>
+  </si>
+  <si>
+    <t>Standard UW Decision</t>
+  </si>
+  <si>
+    <t>Galway</t>
+  </si>
+  <si>
+    <t>AIBL-2026-267355</t>
+  </si>
+  <si>
+    <t>Financial UW</t>
+  </si>
+  <si>
+    <t>Completed - Manual</t>
+  </si>
+  <si>
+    <t>AIBL-2026-888542</t>
+  </si>
+  <si>
+    <t>AIBL-2026-708682</t>
+  </si>
+  <si>
+    <t>AIBL-2026-658314</t>
+  </si>
+  <si>
     <t>Cork</t>
   </si>
   <si>
-    <t>AIBL-2026-202017</t>
-  </si>
-  <si>
-    <t>Completed - Manual</t>
-  </si>
-  <si>
-    <t>AIBL-2026-371527</t>
-  </si>
-  <si>
-    <t>AIBL-2026-485652</t>
-  </si>
-  <si>
-    <t>Underwriting</t>
+    <t>AIBL-2026-541006</t>
+  </si>
+  <si>
+    <t>Claim</t>
+  </si>
+  <si>
+    <t>Income Protection Claim</t>
+  </si>
+  <si>
+    <t>AIBL-2026-999950</t>
+  </si>
+  <si>
+    <t>Endorsement</t>
+  </si>
+  <si>
+    <t>Premium Frequency Change</t>
+  </si>
+  <si>
+    <t>AIBL-2026-390952</t>
+  </si>
+  <si>
+    <t>Beneficiary Change</t>
+  </si>
+  <si>
+    <t>AIBL-2026-302412</t>
+  </si>
+  <si>
+    <t>Address Change</t>
+  </si>
+  <si>
+    <t>AIBL-2026-979774</t>
+  </si>
+  <si>
+    <t>Sum Assured Alteration</t>
+  </si>
+  <si>
+    <t>AIBL-2026-802124</t>
+  </si>
+  <si>
+    <t>AIBL-2026-892525</t>
+  </si>
+  <si>
+    <t>AIBL-2026-488225</t>
+  </si>
+  <si>
+    <t>AIBL-2026-807076</t>
+  </si>
+  <si>
+    <t>AIBL-2026-548558</t>
+  </si>
+  <si>
+    <t>AIBL-2026-103844</t>
+  </si>
+  <si>
+    <t>AIBL-2026-570275</t>
+  </si>
+  <si>
+    <t>Maturity Claim</t>
+  </si>
+  <si>
+    <t>AIBL-2026-213939</t>
+  </si>
+  <si>
+    <t>AIBL-2026-558740</t>
   </si>
   <si>
     <t>Medical UW</t>
   </si>
   <si>
-    <t>Galway</t>
-  </si>
-  <si>
-    <t>AIBL-2026-237887</t>
-  </si>
-  <si>
-    <t>Financial UW</t>
-  </si>
-  <si>
-    <t>Limerick</t>
-  </si>
-  <si>
-    <t>AIBL-2026-649316</t>
-  </si>
-  <si>
-    <t>AIBL-2026-583343</t>
-  </si>
-  <si>
-    <t>Claim</t>
+    <t>AIBL-2026-591990</t>
+  </si>
+  <si>
+    <t>AIBL-2026-347861</t>
+  </si>
+  <si>
+    <t>AIBL-2026-197144</t>
+  </si>
+  <si>
+    <t>AIBL-2026-709530</t>
+  </si>
+  <si>
+    <t>AIBL-2026-212554</t>
+  </si>
+  <si>
+    <t>AIBL-2026-386497</t>
+  </si>
+  <si>
+    <t>AIBL-2026-631089</t>
+  </si>
+  <si>
+    <t>AIBL-2026-414463</t>
+  </si>
+  <si>
+    <t>AIBL-2026-288957</t>
+  </si>
+  <si>
+    <t>AIBL-2026-727410</t>
+  </si>
+  <si>
+    <t>AIBL-2026-283211</t>
+  </si>
+  <si>
+    <t>AIBL-2026-402523</t>
+  </si>
+  <si>
+    <t>Death Claim</t>
+  </si>
+  <si>
+    <t>AIBL-2026-687894</t>
+  </si>
+  <si>
+    <t>AIBL-2026-411641</t>
+  </si>
+  <si>
+    <t>AIBL-2026-231881</t>
+  </si>
+  <si>
+    <t>AIBL-2026-445232</t>
+  </si>
+  <si>
+    <t>Completed - Rework Required</t>
+  </si>
+  <si>
+    <t>AIBL-2026-632052</t>
+  </si>
+  <si>
+    <t>AIBL-2026-643034</t>
+  </si>
+  <si>
+    <t>AIBL-2026-858351</t>
+  </si>
+  <si>
+    <t>AIBL-2026-635819</t>
+  </si>
+  <si>
+    <t>AIBL-2026-832344</t>
+  </si>
+  <si>
+    <t>AIBL-2026-817525</t>
+  </si>
+  <si>
+    <t>AIBL-2026-705426</t>
+  </si>
+  <si>
+    <t>AIBL-2026-125730</t>
+  </si>
+  <si>
+    <t>AIBL-2026-224041</t>
+  </si>
+  <si>
+    <t>AIBL-2026-789943</t>
+  </si>
+  <si>
+    <t>AIBL-2026-474720</t>
+  </si>
+  <si>
+    <t>AIBL-2026-378103</t>
   </si>
   <si>
     <t>Critical Illness Claim</t>
   </si>
   <si>
-    <t>AIBL-2026-640846</t>
-  </si>
-  <si>
-    <t>Endorsement</t>
-  </si>
-  <si>
-    <t>Premium Frequency Change</t>
-  </si>
-  <si>
-    <t>AIBL-2026-979774</t>
-  </si>
-  <si>
-    <t>Sum Assured Alteration</t>
-  </si>
-  <si>
-    <t>AIBL-2026-948936</t>
-  </si>
-  <si>
-    <t>Address Change</t>
-  </si>
-  <si>
-    <t>AIBL-2026-187336</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>AIBL-2026-548558</t>
-  </si>
-  <si>
-    <t>AIBL-2026-103844</t>
-  </si>
-  <si>
-    <t>AIBL-2026-264948</t>
-  </si>
-  <si>
-    <t>AIBL-2026-414916</t>
-  </si>
-  <si>
-    <t>AIBL-2026-902505</t>
-  </si>
-  <si>
-    <t>AIBL-2026-714000</t>
-  </si>
-  <si>
-    <t>Policy Issuance - Single Premium</t>
-  </si>
-  <si>
-    <t>AIBL-2026-213939</t>
-  </si>
-  <si>
-    <t>AIBL-2026-628358</t>
-  </si>
-  <si>
-    <t>AIBL-2026-558740</t>
-  </si>
-  <si>
-    <t>AIBL-2026-373320</t>
-  </si>
-  <si>
-    <t>Standard UW Decision</t>
-  </si>
-  <si>
-    <t>AIBL-2026-522871</t>
-  </si>
-  <si>
-    <t>AIBL-2026-709530</t>
-  </si>
-  <si>
-    <t>AIBL-2026-140064</t>
-  </si>
-  <si>
-    <t>AIBL-2026-924132</t>
-  </si>
-  <si>
-    <t>AIBL-2026-176142</t>
-  </si>
-  <si>
-    <t>AIBL-2026-901051</t>
-  </si>
-  <si>
-    <t>AIBL-2026-669608</t>
-  </si>
-  <si>
-    <t>AIBL-2026-727410</t>
-  </si>
-  <si>
-    <t>AIBL-2026-919735</t>
-  </si>
-  <si>
-    <t>AIBL-2026-687894</t>
-  </si>
-  <si>
-    <t>AIBL-2026-315745</t>
-  </si>
-  <si>
-    <t>AIBL-2026-411641</t>
-  </si>
-  <si>
-    <t>AIBL-2026-890238</t>
-  </si>
-  <si>
-    <t>AIBL-2026-903005</t>
-  </si>
-  <si>
-    <t>AIBL-2026-988471</t>
-  </si>
-  <si>
-    <t>AIBL-2026-722413</t>
-  </si>
-  <si>
-    <t>AIBL-2026-827928</t>
-  </si>
-  <si>
-    <t>AIBL-2026-751935</t>
-  </si>
-  <si>
-    <t>AIBL-2026-658812</t>
-  </si>
-  <si>
-    <t>AIBL-2026-855653</t>
-  </si>
-  <si>
-    <t>AIBL-2026-224041</t>
-  </si>
-  <si>
-    <t>AIBL-2026-698367</t>
-  </si>
-  <si>
-    <t>AIBL-2026-853300</t>
-  </si>
-  <si>
-    <t>Income Protection Claim</t>
+    <t>AIBL-2026-507843</t>
   </si>
   <si>
     <t>AIBL-2026-669471</t>
   </si>
   <si>
-    <t>AIBL-2026-501932</t>
-  </si>
-  <si>
-    <t>Beneficiary Change</t>
-  </si>
-  <si>
-    <t>AIBL-2026-439120</t>
-  </si>
-  <si>
-    <t>AIBL-2026-624311</t>
-  </si>
-  <si>
-    <t>AIBL-2026-888087</t>
-  </si>
-  <si>
-    <t>AIBL-2026-665205</t>
+    <t>AIBL-2026-330649</t>
+  </si>
+  <si>
+    <t>AIBL-2026-766109</t>
+  </si>
+  <si>
+    <t>AIBL-2026-163134</t>
+  </si>
+  <si>
+    <t>AIBL-2026-626275</t>
+  </si>
+  <si>
+    <t>AIBL-2026-254407</t>
+  </si>
+  <si>
+    <t>AIBL-2026-181127</t>
   </si>
   <si>
     <t>AIBL-2026-311919</t>
   </si>
   <si>
-    <t>AIBL-2026-265254</t>
-  </si>
-  <si>
-    <t>Maturity Claim</t>
-  </si>
-  <si>
-    <t>AIBL-2026-493375</t>
-  </si>
-  <si>
-    <t>AIBL-2026-748618</t>
+    <t>AIBL-2026-135495</t>
+  </si>
+  <si>
+    <t>AIBL-2026-887301</t>
+  </si>
+  <si>
+    <t>AIBL-2026-448437</t>
   </si>
   <si>
     <t>AIBL-2026-561761</t>
   </si>
   <si>
-    <t>AIBL-2026-456559</t>
-  </si>
-  <si>
-    <t>AIBL-2026-864267</t>
-  </si>
-  <si>
-    <t>AIBL-2026-924929</t>
-  </si>
-  <si>
-    <t>AIBL-2026-552182</t>
-  </si>
-  <si>
-    <t>AIBL-2026-836785</t>
-  </si>
-  <si>
-    <t>AIBL-2026-807620</t>
-  </si>
-  <si>
-    <t>AIBL-2026-521110</t>
-  </si>
-  <si>
-    <t>AIBL-2026-140582</t>
-  </si>
-  <si>
-    <t>AIBL-2026-443183</t>
-  </si>
-  <si>
-    <t>AIBL-2026-872156</t>
-  </si>
-  <si>
-    <t>AIBL-2026-999438</t>
+    <t>AIBL-2026-744635</t>
+  </si>
+  <si>
+    <t>AIBL-2026-455550</t>
+  </si>
+  <si>
+    <t>AIBL-2026-440827</t>
+  </si>
+  <si>
+    <t>AIBL-2026-468617</t>
+  </si>
+  <si>
+    <t>AIBL-2026-218880</t>
+  </si>
+  <si>
+    <t>AIBL-2026-970613</t>
+  </si>
+  <si>
+    <t>AIBL-2026-937039</t>
   </si>
   <si>
     <t>AIBL-2026-591728</t>
   </si>
   <si>
-    <t>AIBL-2026-108169</t>
+    <t>AIBL-2026-485666</t>
   </si>
   <si>
     <t>AIBL-2026-296792</t>
   </si>
   <si>
-    <t>AIBL-2026-307076</t>
+    <t>AIBL-2026-671386</t>
   </si>
   <si>
     <t>AIBL-2026-552680</t>
   </si>
   <si>
-    <t>AIBL-2026-266361</t>
-  </si>
-  <si>
-    <t>AIBL-2026-908220</t>
-  </si>
-  <si>
-    <t>AIBL-2026-287722</t>
-  </si>
-  <si>
-    <t>AIBL-2026-104684</t>
-  </si>
-  <si>
     <t>AIBL-2026-570465</t>
   </si>
   <si>
+    <t>AIBL-2026-452435</t>
+  </si>
+  <si>
     <t>AIBL-2026-116490</t>
   </si>
   <si>
-    <t>AIBL-2026-992768</t>
-  </si>
-  <si>
-    <t>AIBL-2026-148924</t>
+    <t>AIBL-2026-505300</t>
+  </si>
+  <si>
+    <t>AIBL-2026-531842</t>
   </si>
   <si>
     <t>AIBL-2026-773204</t>
   </si>
   <si>
-    <t>AIBL-2026-464997</t>
+    <t>AIBL-2026-909275</t>
+  </si>
+  <si>
+    <t>AIBL-2026-894873</t>
   </si>
   <si>
     <t>AIBL-2026-452353</t>
   </si>
   <si>
-    <t>AIBL-2026-398923</t>
+    <t>AIBL-2026-540807</t>
+  </si>
+  <si>
+    <t>AIBL-2026-816844</t>
+  </si>
+  <si>
+    <t>AIBL-2026-459795</t>
   </si>
   <si>
     <t>AIBL-2026-411464</t>
@@ -371,202 +389,178 @@
     <t>AIBL-2026-537936</t>
   </si>
   <si>
-    <t>AIBL-2026-727896</t>
-  </si>
-  <si>
-    <t>AIBL-2026-374845</t>
-  </si>
-  <si>
-    <t>AIBL-2026-513504</t>
+    <t>AIBL-2026-780554</t>
+  </si>
+  <si>
+    <t>AIBL-2026-473199</t>
+  </si>
+  <si>
+    <t>AIBL-2026-954125</t>
   </si>
   <si>
     <t>AIBL-2026-258412</t>
   </si>
   <si>
-    <t>AIBL-2026-559115</t>
-  </si>
-  <si>
-    <t>AIBL-2026-701930</t>
-  </si>
-  <si>
-    <t>AIBL-2026-241601</t>
-  </si>
-  <si>
-    <t>AIBL-2026-150481</t>
-  </si>
-  <si>
-    <t>AIBL-2026-930833</t>
-  </si>
-  <si>
-    <t>AIBL-2026-548555</t>
-  </si>
-  <si>
-    <t>AIBL-2026-737310</t>
-  </si>
-  <si>
-    <t>AIBL-2026-758214</t>
-  </si>
-  <si>
-    <t>AIBL-2026-286032</t>
-  </si>
-  <si>
-    <t>AIBL-2026-858943</t>
-  </si>
-  <si>
-    <t>Death Claim</t>
-  </si>
-  <si>
-    <t>AIBL-2026-716383</t>
-  </si>
-  <si>
-    <t>AIBL-2026-742105</t>
+    <t>AIBL-2026-217371</t>
+  </si>
+  <si>
+    <t>AIBL-2026-976620</t>
+  </si>
+  <si>
+    <t>AIBL-2026-616675</t>
+  </si>
+  <si>
+    <t>AIBL-2026-871271</t>
+  </si>
+  <si>
+    <t>AIBL-2026-154458</t>
+  </si>
+  <si>
+    <t>AIBL-2026-373751</t>
+  </si>
+  <si>
+    <t>AIBL-2026-633858</t>
+  </si>
+  <si>
+    <t>AIBL-2026-408133</t>
+  </si>
+  <si>
+    <t>AIBL-2026-563579</t>
   </si>
   <si>
     <t>AIBL-2026-858790</t>
   </si>
   <si>
-    <t>AIBL-2026-332315</t>
-  </si>
-  <si>
     <t>AIBL-2026-869640</t>
   </si>
   <si>
-    <t>AIBL-2026-662048</t>
-  </si>
-  <si>
-    <t>AIBL-2026-632149</t>
-  </si>
-  <si>
-    <t>AIBL-2026-883719</t>
-  </si>
-  <si>
-    <t>AIBL-2026-474294</t>
-  </si>
-  <si>
-    <t>AIBL-2026-445376</t>
+    <t>AIBL-2026-749387</t>
+  </si>
+  <si>
+    <t>AIBL-2026-551233</t>
+  </si>
+  <si>
+    <t>AIBL-2026-339940</t>
+  </si>
+  <si>
+    <t>AIBL-2026-741855</t>
+  </si>
+  <si>
+    <t>AIBL-2026-281113</t>
   </si>
   <si>
     <t>AIBL-2026-602141</t>
   </si>
   <si>
-    <t>AIBL-2026-235092</t>
-  </si>
-  <si>
-    <t>AIBL-2026-849690</t>
-  </si>
-  <si>
-    <t>AIBL-2026-464656</t>
-  </si>
-  <si>
-    <t>AIBL-2026-107721</t>
+    <t>AIBL-2026-978285</t>
+  </si>
+  <si>
+    <t>AIBL-2026-862337</t>
+  </si>
+  <si>
+    <t>AIBL-2026-796283</t>
+  </si>
+  <si>
+    <t>AIBL-2026-526553</t>
   </si>
   <si>
     <t>AIBL-2026-430755</t>
   </si>
   <si>
-    <t>AIBL-2026-518197</t>
-  </si>
-  <si>
-    <t>AIBL-2026-945753</t>
+    <t>AIBL-2026-902169</t>
+  </si>
+  <si>
+    <t>AIBL-2026-447138</t>
+  </si>
+  <si>
+    <t>AIBL-2026-468930</t>
+  </si>
+  <si>
+    <t>AIBL-2026-332074</t>
   </si>
   <si>
     <t>AIBL-2026-510546</t>
   </si>
   <si>
-    <t>Completed - Rework Required</t>
-  </si>
-  <si>
-    <t>AIBL-2026-362886</t>
+    <t>AIBL-2026-210890</t>
+  </si>
+  <si>
+    <t>AIBL-2026-986784</t>
   </si>
   <si>
     <t>AIBL-2026-129774</t>
   </si>
   <si>
+    <t>AIBL-2026-170137</t>
+  </si>
+  <si>
     <t>AIBL-2026-860092</t>
   </si>
   <si>
-    <t>AIBL-2026-418419</t>
-  </si>
-  <si>
-    <t>AIBL-2026-137348</t>
-  </si>
-  <si>
-    <t>AIBL-2026-412928</t>
-  </si>
-  <si>
-    <t>AIBL-2026-158793</t>
+    <t>AIBL-2026-663078</t>
   </si>
   <si>
     <t>AIBL-2026-216291</t>
   </si>
   <si>
-    <t>AIBL-2026-209715</t>
-  </si>
-  <si>
-    <t>AIBL-2026-871680</t>
-  </si>
-  <si>
     <t>AIBL-2026-864477</t>
   </si>
   <si>
-    <t>AIBL-2026-905837</t>
-  </si>
-  <si>
-    <t>AIBL-2026-756212</t>
-  </si>
-  <si>
-    <t>AIBL-2026-320516</t>
-  </si>
-  <si>
-    <t>AIBL-2026-352353</t>
+    <t>AIBL-2026-617782</t>
+  </si>
+  <si>
+    <t>AIBL-2026-241310</t>
   </si>
   <si>
     <t>AIBL-2026-434682</t>
   </si>
   <si>
-    <t>AIBL-2026-355849</t>
-  </si>
-  <si>
-    <t>AIBL-2026-538501</t>
-  </si>
-  <si>
-    <t>AIBL-2026-778732</t>
-  </si>
-  <si>
-    <t>AIBL-2026-955365</t>
-  </si>
-  <si>
-    <t>AIBL-2026-540742</t>
-  </si>
-  <si>
-    <t>AIBL-2026-650156</t>
-  </si>
-  <si>
-    <t>AIBL-2026-777790</t>
-  </si>
-  <si>
-    <t>AIBL-2026-574299</t>
-  </si>
-  <si>
-    <t>AIBL-2026-387095</t>
-  </si>
-  <si>
-    <t>AIBL-2026-290327</t>
-  </si>
-  <si>
-    <t>AIBL-2026-494570</t>
-  </si>
-  <si>
-    <t>AIBL-2026-119289</t>
-  </si>
-  <si>
-    <t>AIBL-2026-272643</t>
-  </si>
-  <si>
-    <t>AIBL-2026-106759</t>
-  </si>
-  <si>
-    <t>AIBL-2026-426073</t>
+    <t>AIBL-2026-463132</t>
+  </si>
+  <si>
+    <t>AIBL-2026-184594</t>
+  </si>
+  <si>
+    <t>AIBL-2026-993014</t>
+  </si>
+  <si>
+    <t>AIBL-2026-281153</t>
+  </si>
+  <si>
+    <t>AIBL-2026-598846</t>
+  </si>
+  <si>
+    <t>AIBL-2026-183938</t>
+  </si>
+  <si>
+    <t>AIBL-2026-778169</t>
+  </si>
+  <si>
+    <t>AIBL-2026-109123</t>
+  </si>
+  <si>
+    <t>AIBL-2026-949999</t>
+  </si>
+  <si>
+    <t>AIBL-2026-812483</t>
+  </si>
+  <si>
+    <t>AIBL-2026-986995</t>
+  </si>
+  <si>
+    <t>AIBL-2026-461430</t>
+  </si>
+  <si>
+    <t>AIBL-2026-450708</t>
+  </si>
+  <si>
+    <t>AIBL-2026-709838</t>
+  </si>
+  <si>
+    <t>AIBL-2026-899668</t>
+  </si>
+  <si>
+    <t>AIBL-2026-692887</t>
   </si>
   <si>
     <t>AIBL-2026-366090</t>
@@ -578,55 +572,58 @@
     <t>AIBL-2026-876353</t>
   </si>
   <si>
-    <t>AIBL-2026-688328</t>
-  </si>
-  <si>
-    <t>AIBL-2026-237626</t>
+    <t>AIBL-2026-376341</t>
+  </si>
+  <si>
+    <t>AIBL-2026-562770</t>
+  </si>
+  <si>
+    <t>AIBL-2026-373373</t>
   </si>
   <si>
     <t>AIBL-2026-366426</t>
   </si>
   <si>
-    <t>AIBL-2026-882310</t>
-  </si>
-  <si>
-    <t>AIBL-2026-652778</t>
-  </si>
-  <si>
-    <t>AIBL-2026-812905</t>
-  </si>
-  <si>
-    <t>AIBL-2026-217541</t>
-  </si>
-  <si>
-    <t>AIBL-2026-208082</t>
-  </si>
-  <si>
-    <t>AIBL-2026-179256</t>
-  </si>
-  <si>
-    <t>AIBL-2026-400318</t>
-  </si>
-  <si>
-    <t>AIBL-2026-292848</t>
-  </si>
-  <si>
-    <t>AIBL-2026-982154</t>
-  </si>
-  <si>
-    <t>AIBL-2026-366305</t>
-  </si>
-  <si>
-    <t>AIBL-2026-288204</t>
-  </si>
-  <si>
-    <t>AIBL-2026-254526</t>
-  </si>
-  <si>
-    <t>AIBL-2026-563328</t>
-  </si>
-  <si>
-    <t>AIBL-2026-637194</t>
+    <t>AIBL-2026-705555</t>
+  </si>
+  <si>
+    <t>AIBL-2026-950322</t>
+  </si>
+  <si>
+    <t>AIBL-2026-727837</t>
+  </si>
+  <si>
+    <t>AIBL-2026-710877</t>
+  </si>
+  <si>
+    <t>AIBL-2026-525139</t>
+  </si>
+  <si>
+    <t>AIBL-2026-450094</t>
+  </si>
+  <si>
+    <t>AIBL-2026-716581</t>
+  </si>
+  <si>
+    <t>AIBL-2026-665385</t>
+  </si>
+  <si>
+    <t>AIBL-2026-489649</t>
+  </si>
+  <si>
+    <t>AIBL-2026-828147</t>
+  </si>
+  <si>
+    <t>AIBL-2026-410538</t>
+  </si>
+  <si>
+    <t>AIBL-2026-310033</t>
+  </si>
+  <si>
+    <t>AIBL-2026-315494</t>
+  </si>
+  <si>
+    <t>AIBL-2026-508957</t>
   </si>
   <si>
     <t>AIBL-2026-892009</t>
@@ -635,55 +632,58 @@
     <t>AIBL-2026-597197</t>
   </si>
   <si>
-    <t>AIBL-2026-497858</t>
-  </si>
-  <si>
-    <t>AIBL-2026-207596</t>
-  </si>
-  <si>
-    <t>AIBL-2026-739550</t>
-  </si>
-  <si>
-    <t>AIBL-2026-782677</t>
+    <t>AIBL-2026-557300</t>
+  </si>
+  <si>
+    <t>AIBL-2026-275780</t>
+  </si>
+  <si>
+    <t>AIBL-2026-674630</t>
   </si>
   <si>
     <t>AIBL-2026-262630</t>
   </si>
   <si>
+    <t>AIBL-2026-355190</t>
+  </si>
+  <si>
+    <t>AIBL-2026-851729</t>
+  </si>
+  <si>
+    <t>AIBL-2026-428703</t>
+  </si>
+  <si>
     <t>AIBL-2026-318340</t>
   </si>
   <si>
-    <t>AIBL-2026-929128</t>
-  </si>
-  <si>
-    <t>AIBL-2026-990014</t>
-  </si>
-  <si>
-    <t>AIBL-2026-662419</t>
+    <t>AIBL-2026-731728</t>
+  </si>
+  <si>
+    <t>AIBL-2026-730756</t>
+  </si>
+  <si>
+    <t>AIBL-2026-743570</t>
   </si>
   <si>
     <t>AIBL-2026-128711</t>
   </si>
   <si>
-    <t>AIBL-2026-504081</t>
+    <t>AIBL-2026-780557</t>
+  </si>
+  <si>
+    <t>AIBL-2026-525750</t>
   </si>
   <si>
     <t>AIBL-2026-267623</t>
   </si>
   <si>
-    <t>AIBL-2026-781260</t>
-  </si>
-  <si>
-    <t>AIBL-2026-846095</t>
-  </si>
-  <si>
-    <t>AIBL-2026-593836</t>
+    <t>AIBL-2026-987869</t>
   </si>
   <si>
     <t>AIBL-2026-600198</t>
   </si>
   <si>
-    <t>AIBL-2026-952949</t>
+    <t>AIBL-2026-923838</t>
   </si>
   <si>
     <t>Source System</t>
@@ -1179,10 +1179,10 @@
         <v>46237</v>
       </c>
       <c r="E2" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F2" s="2">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -1208,102 +1208,102 @@
         <v>46239</v>
       </c>
       <c r="F3" s="2">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1">
         <v>46237</v>
       </c>
       <c r="E4" s="1">
-        <v>46243</v>
+        <v>46240</v>
       </c>
       <c r="F4" s="2">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
       </c>
       <c r="D5" s="1">
         <v>46237</v>
       </c>
       <c r="E5" s="1">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="F5" s="2">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1">
         <v>46237</v>
       </c>
       <c r="E6" s="1">
-        <v>46242</v>
+        <v>46240</v>
       </c>
       <c r="F6" s="2">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="1">
         <v>46237</v>
@@ -1312,125 +1312,125 @@
         <v>46239</v>
       </c>
       <c r="F7" s="2">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D8" s="1">
         <v>46237</v>
       </c>
       <c r="E8" s="1">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="F8" s="2">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1">
         <v>46237</v>
       </c>
       <c r="E9" s="1">
-        <v>46251</v>
+        <v>46240</v>
       </c>
       <c r="F9" s="2">
-        <v>14.2</v>
+        <v>3.4</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D10" s="1">
         <v>46237</v>
       </c>
       <c r="E10" s="1">
-        <v>46239</v>
+        <v>46243</v>
       </c>
       <c r="F10" s="2">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H10" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
         <v>33</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
       </c>
       <c r="D11" s="1">
         <v>46237</v>
       </c>
       <c r="E11" s="1">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="F11" s="2">
-        <v>2.6</v>
+        <v>8.3</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
         <v>35</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
       </c>
       <c r="C12" t="s">
         <v>36</v>
@@ -1442,13 +1442,13 @@
         <v>46239</v>
       </c>
       <c r="F12" s="2">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G12" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H12" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1456,25 +1456,25 @@
         <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D13" s="1">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="E13" s="1">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="F13" s="2">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="G13" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H13" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1482,201 +1482,201 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D14" s="1">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="E14" s="1">
-        <v>46244</v>
+        <v>46239</v>
       </c>
       <c r="F14" s="2">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
       </c>
       <c r="H14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D15" s="1">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="E15" s="1">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="F15" s="2">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
       </c>
       <c r="H15" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D16" s="1">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="E16" s="1">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="F16" s="2">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="G16" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H16" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
         <v>42</v>
       </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" t="s">
-        <v>21</v>
-      </c>
       <c r="D17" s="1">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="E17" s="1">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="F17" s="2">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="G17" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H17" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D18" s="1">
         <v>46238</v>
       </c>
       <c r="E18" s="1">
-        <v>46243</v>
+        <v>46241</v>
       </c>
       <c r="F18" s="2">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
       </c>
       <c r="H18" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="D19" s="1">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="E19" s="1">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="F19" s="2">
-        <v>6.7</v>
+        <v>3.8</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
       </c>
       <c r="H19" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D20" s="1">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="E20" s="1">
-        <v>46245</v>
+        <v>46242</v>
       </c>
       <c r="F20" s="2">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="G20" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H20" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D21" s="1">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="E21" s="1">
         <v>46241</v>
       </c>
       <c r="F21" s="2">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="G21" t="s">
         <v>11</v>
@@ -1687,39 +1687,39 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="D22" s="1">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="E22" s="1">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="F22" s="2">
-        <v>2.3</v>
+        <v>9.5</v>
       </c>
       <c r="G22" t="s">
         <v>11</v>
       </c>
       <c r="H22" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D23" s="1">
         <v>46239</v>
@@ -1728,232 +1728,232 @@
         <v>46243</v>
       </c>
       <c r="F23" s="2">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="G23" t="s">
         <v>11</v>
       </c>
       <c r="H23" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D24" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E24" s="1">
         <v>46240</v>
       </c>
-      <c r="E24" s="1">
-        <v>46243</v>
-      </c>
       <c r="F24" s="2">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="G24" t="s">
         <v>11</v>
       </c>
       <c r="H24" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D25" s="1">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="E25" s="1">
-        <v>46246</v>
+        <v>46255</v>
       </c>
       <c r="F25" s="2">
-        <v>6.3</v>
+        <v>16.2</v>
       </c>
       <c r="G25" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H25" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D26" s="1">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="E26" s="1">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="F26" s="2">
-        <v>17.9</v>
+        <v>4.9</v>
       </c>
       <c r="G26" t="s">
         <v>11</v>
       </c>
       <c r="H26" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D27" s="1">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="E27" s="1">
         <v>46244</v>
       </c>
       <c r="F27" s="2">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="G27" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H27" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D28" s="1">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="E28" s="1">
         <v>46246</v>
       </c>
       <c r="F28" s="2">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="G28" t="s">
         <v>11</v>
       </c>
       <c r="H28" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D29" s="1">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="E29" s="1">
-        <v>46246</v>
+        <v>46243</v>
       </c>
       <c r="F29" s="2">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="G29" t="s">
         <v>11</v>
       </c>
       <c r="H29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
         <v>50</v>
       </c>
       <c r="D30" s="1">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="E30" s="1">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="F30" s="2">
-        <v>5.2</v>
+        <v>11.3</v>
       </c>
       <c r="G30" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H30" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D31" s="1">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="E31" s="1">
         <v>46243</v>
       </c>
       <c r="F31" s="2">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="G31" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H31" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B32" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D32" s="1">
         <v>46241</v>
@@ -1962,24 +1962,24 @@
         <v>46245</v>
       </c>
       <c r="F32" s="2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="G32" t="s">
         <v>11</v>
       </c>
       <c r="H32" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D33" s="1">
         <v>46241</v>
@@ -1988,24 +1988,24 @@
         <v>46245</v>
       </c>
       <c r="F33" s="2">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="G33" t="s">
         <v>11</v>
       </c>
       <c r="H33" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D34" s="1">
         <v>46241</v>
@@ -2014,148 +2014,148 @@
         <v>46244</v>
       </c>
       <c r="F34" s="2">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="G34" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H34" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D35" s="1">
         <v>46241</v>
       </c>
       <c r="E35" s="1">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="F35" s="2">
-        <v>3.7</v>
+        <v>6.7</v>
       </c>
       <c r="G35" t="s">
         <v>11</v>
       </c>
       <c r="H35" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B36" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="D36" s="1">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="E36" s="1">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="F36" s="2">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
       <c r="G36" t="s">
         <v>11</v>
       </c>
       <c r="H36" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="D37" s="1">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="E37" s="1">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="F37" s="2">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="G37" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H37" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D38" s="1">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="E38" s="1">
-        <v>46248</v>
+        <v>46243</v>
       </c>
       <c r="F38" s="2">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="G38" t="s">
         <v>11</v>
       </c>
       <c r="H38" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D39" s="1">
         <v>46244</v>
       </c>
       <c r="E39" s="1">
-        <v>46250</v>
+        <v>46246</v>
       </c>
       <c r="F39" s="2">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="G39" t="s">
         <v>11</v>
       </c>
       <c r="H39" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
@@ -2170,102 +2170,102 @@
         <v>46246</v>
       </c>
       <c r="F40" s="2">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="G40" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="H40" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
       </c>
       <c r="C41" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="D41" s="1">
         <v>46244</v>
       </c>
       <c r="E41" s="1">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="F41" s="2">
-        <v>4.4</v>
+        <v>6.9</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
       </c>
       <c r="H41" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B42" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C42" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D42" s="1">
         <v>46244</v>
       </c>
       <c r="E42" s="1">
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="F42" s="2">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
       </c>
       <c r="H42" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D43" s="1">
         <v>46244</v>
       </c>
       <c r="E43" s="1">
-        <v>46246</v>
+        <v>46249</v>
       </c>
       <c r="F43" s="2">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="G43" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H43" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D44" s="1">
         <v>46244</v>
@@ -2274,218 +2274,218 @@
         <v>46246</v>
       </c>
       <c r="F44" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G44" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H44" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D45" s="1">
         <v>46244</v>
       </c>
       <c r="E45" s="1">
-        <v>46257</v>
+        <v>46247</v>
       </c>
       <c r="F45" s="2">
-        <v>12.6</v>
+        <v>2.5</v>
       </c>
       <c r="G45" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H45" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C46" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="D46" s="1">
         <v>46244</v>
       </c>
       <c r="E46" s="1">
-        <v>46254</v>
+        <v>46251</v>
       </c>
       <c r="F46" s="2">
-        <v>9.7</v>
+        <v>7.2</v>
       </c>
       <c r="G46" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H46" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C47" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="D47" s="1">
         <v>46244</v>
       </c>
       <c r="E47" s="1">
-        <v>46254</v>
+        <v>46248</v>
       </c>
       <c r="F47" s="2">
-        <v>10.2</v>
+        <v>3.7</v>
       </c>
       <c r="G47" t="s">
         <v>11</v>
       </c>
       <c r="H47" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C48" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D48" s="1">
         <v>46244</v>
       </c>
       <c r="E48" s="1">
-        <v>46249</v>
+        <v>46248</v>
       </c>
       <c r="F48" s="2">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="G48" t="s">
         <v>11</v>
       </c>
       <c r="H48" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C49" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D49" s="1">
+        <v>46244</v>
+      </c>
+      <c r="E49" s="1">
         <v>46245</v>
       </c>
-      <c r="E49" s="1">
-        <v>46251</v>
-      </c>
       <c r="F49" s="2">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="G49" t="s">
         <v>11</v>
       </c>
       <c r="H49" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D50" s="1">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="E50" s="1">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="F50" s="2">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="G50" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H50" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B51" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D51" s="1">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="E51" s="1">
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="F51" s="2">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="G51" t="s">
         <v>11</v>
       </c>
       <c r="H51" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B52" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C52" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="D52" s="1">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="E52" s="1">
-        <v>46247</v>
+        <v>46261</v>
       </c>
       <c r="F52" s="2">
-        <v>1.8</v>
+        <v>16.7</v>
       </c>
       <c r="G52" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H52" t="s">
         <v>12</v>
@@ -2493,259 +2493,259 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D53" s="1">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="E53" s="1">
-        <v>46250</v>
+        <v>46259</v>
       </c>
       <c r="F53" s="2">
-        <v>4.8</v>
+        <v>15.1</v>
       </c>
       <c r="G53" t="s">
         <v>11</v>
       </c>
       <c r="H53" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C54" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D54" s="1">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="E54" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="F54" s="2">
-        <v>8.8</v>
+        <v>8.6</v>
       </c>
       <c r="G54" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H54" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B55" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="D55" s="1">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="E55" s="1">
-        <v>46250</v>
+        <v>46246</v>
       </c>
       <c r="F55" s="2">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="G55" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H55" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B56" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C56" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="D56" s="1">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="E56" s="1">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="F56" s="2">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="G56" t="s">
         <v>11</v>
       </c>
       <c r="H56" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B57" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C57" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D57" s="1">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="E57" s="1">
-        <v>46249</v>
+        <v>46246</v>
       </c>
       <c r="F57" s="2">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="G57" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="H57" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B58" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="D58" s="1">
         <v>46245</v>
       </c>
       <c r="E58" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="F58" s="2">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="G58" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H58" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B59" t="s">
         <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D59" s="1">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="E59" s="1">
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="F59" s="2">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="G59" t="s">
         <v>11</v>
       </c>
       <c r="H59" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B60" t="s">
         <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D60" s="1">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="E60" s="1">
-        <v>46252</v>
+        <v>46249</v>
       </c>
       <c r="F60" s="2">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="G60" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H60" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B61" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D61" s="1">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="E61" s="1">
         <v>46251</v>
       </c>
       <c r="F61" s="2">
-        <v>4.7</v>
+        <v>6.1</v>
       </c>
       <c r="G61" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H61" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C62" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D62" s="1">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="E62" s="1">
-        <v>46249</v>
+        <v>46247</v>
       </c>
       <c r="F62" s="2">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G62" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H62" t="s">
         <v>12</v>
@@ -2753,360 +2753,360 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B63" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C63" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="D63" s="1">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="E63" s="1">
-        <v>46259</v>
+        <v>46257</v>
       </c>
       <c r="F63" s="2">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="G63" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H63" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B64" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C64" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D64" s="1">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="E64" s="1">
-        <v>46264</v>
+        <v>46254</v>
       </c>
       <c r="F64" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G64" t="s">
         <v>11</v>
       </c>
       <c r="H64" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B65" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C65" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D65" s="1">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="E65" s="1">
-        <v>46250</v>
+        <v>46249</v>
       </c>
       <c r="F65" s="2">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="G65" t="s">
         <v>11</v>
       </c>
       <c r="H65" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C66" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D66" s="1">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="E66" s="1">
-        <v>46249</v>
+        <v>46248</v>
       </c>
       <c r="F66" s="2">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="G66" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H66" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B67" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C67" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D67" s="1">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="E67" s="1">
-        <v>46251</v>
+        <v>46249</v>
       </c>
       <c r="F67" s="2">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="G67" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H67" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B68" t="s">
         <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D68" s="1">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="E68" s="1">
-        <v>46253</v>
+        <v>46249</v>
       </c>
       <c r="F68" s="2">
-        <v>6.2</v>
+        <v>2.9</v>
       </c>
       <c r="G68" t="s">
         <v>11</v>
       </c>
       <c r="H68" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B69" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C69" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D69" s="1">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="E69" s="1">
         <v>46249</v>
       </c>
       <c r="F69" s="2">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="G69" t="s">
         <v>11</v>
       </c>
       <c r="H69" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B70" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C70" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D70" s="1">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="E70" s="1">
-        <v>46250</v>
+        <v>46252</v>
       </c>
       <c r="F70" s="2">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="G70" t="s">
         <v>11</v>
       </c>
       <c r="H70" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B71" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C71" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D71" s="1">
+        <v>46246</v>
+      </c>
+      <c r="E71" s="1">
         <v>46247</v>
       </c>
-      <c r="E71" s="1">
-        <v>46251</v>
-      </c>
       <c r="F71" s="2">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="G71" t="s">
         <v>11</v>
       </c>
       <c r="H71" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B72" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D72" s="1">
         <v>46247</v>
       </c>
       <c r="E72" s="1">
-        <v>46261</v>
+        <v>46254</v>
       </c>
       <c r="F72" s="2">
-        <v>13.7</v>
+        <v>7.4</v>
       </c>
       <c r="G72" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H72" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B73" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D73" s="1">
         <v>46247</v>
       </c>
       <c r="E73" s="1">
-        <v>46250</v>
+        <v>46249</v>
       </c>
       <c r="F73" s="2">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="G73" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H73" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B74" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C74" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D74" s="1">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="E74" s="1">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="F74" s="2">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="G74" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H74" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B75" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C75" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D75" s="1">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="E75" s="1">
         <v>46250</v>
       </c>
       <c r="F75" s="2">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="G75" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="H75" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B76" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C76" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D76" s="1">
+        <v>46247</v>
+      </c>
+      <c r="E76" s="1">
         <v>46248</v>
       </c>
-      <c r="E76" s="1">
-        <v>46250</v>
-      </c>
       <c r="F76" s="2">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="G76" t="s">
         <v>11</v>
@@ -3117,241 +3117,241 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B77" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C77" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D77" s="1">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="E77" s="1">
-        <v>46253</v>
+        <v>46250</v>
       </c>
       <c r="F77" s="2">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="G77" t="s">
         <v>11</v>
       </c>
       <c r="H77" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C78" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="D78" s="1">
         <v>46248</v>
       </c>
       <c r="E78" s="1">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F78" s="2">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G78" t="s">
         <v>11</v>
       </c>
       <c r="H78" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B79" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C79" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D79" s="1">
         <v>46248</v>
       </c>
       <c r="E79" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="F79" s="2">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="G79" t="s">
         <v>11</v>
       </c>
       <c r="H79" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B80" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C80" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D80" s="1">
         <v>46248</v>
       </c>
       <c r="E80" s="1">
-        <v>46253</v>
+        <v>46249</v>
       </c>
       <c r="F80" s="2">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="G80" t="s">
         <v>11</v>
       </c>
       <c r="H80" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B81" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C81" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="D81" s="1">
         <v>46248</v>
       </c>
       <c r="E81" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F81" s="2">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="G81" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H81" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B82" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C82" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="D82" s="1">
         <v>46248</v>
       </c>
       <c r="E82" s="1">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="F82" s="2">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="G82" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H82" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B83" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C83" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D83" s="1">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="E83" s="1">
-        <v>46257</v>
+        <v>46250</v>
       </c>
       <c r="F83" s="2">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="G83" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H83" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B84" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C84" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="D84" s="1">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="E84" s="1">
-        <v>46256</v>
+        <v>46253</v>
       </c>
       <c r="F84" s="2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G84" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H84" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B85" t="s">
         <v>9</v>
       </c>
       <c r="C85" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D85" s="1">
         <v>46251</v>
       </c>
       <c r="E85" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="F85" s="2">
-        <v>4.3</v>
+        <v>7.3</v>
       </c>
       <c r="G85" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H85" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B86" t="s">
         <v>9</v>
@@ -3363,73 +3363,73 @@
         <v>46251</v>
       </c>
       <c r="E86" s="1">
-        <v>46257</v>
+        <v>46254</v>
       </c>
       <c r="F86" s="2">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="G86" t="s">
         <v>11</v>
       </c>
       <c r="H86" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B87" t="s">
         <v>9</v>
       </c>
       <c r="C87" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D87" s="1">
         <v>46251</v>
       </c>
       <c r="E87" s="1">
-        <v>46253</v>
+        <v>46256</v>
       </c>
       <c r="F87" s="2">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="G87" t="s">
         <v>11</v>
       </c>
       <c r="H87" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B88" t="s">
         <v>9</v>
       </c>
       <c r="C88" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D88" s="1">
         <v>46251</v>
       </c>
       <c r="E88" s="1">
-        <v>46257</v>
+        <v>46255</v>
       </c>
       <c r="F88" s="2">
-        <v>6.1</v>
+        <v>4.2</v>
       </c>
       <c r="G88" t="s">
         <v>11</v>
       </c>
       <c r="H88" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B89" t="s">
         <v>9</v>
@@ -3441,79 +3441,79 @@
         <v>46251</v>
       </c>
       <c r="E89" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="F89" s="2">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="G89" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H89" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B90" t="s">
         <v>9</v>
       </c>
       <c r="C90" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D90" s="1">
         <v>46251</v>
       </c>
       <c r="E90" s="1">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="F90" s="2">
-        <v>7.3</v>
+        <v>4.4</v>
       </c>
       <c r="G90" t="s">
         <v>11</v>
       </c>
       <c r="H90" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B91" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C91" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D91" s="1">
         <v>46251</v>
       </c>
       <c r="E91" s="1">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="F91" s="2">
-        <v>4.6</v>
+        <v>7.3</v>
       </c>
       <c r="G91" t="s">
         <v>11</v>
       </c>
       <c r="H91" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B92" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C92" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D92" s="1">
         <v>46251</v>
@@ -3522,24 +3522,24 @@
         <v>46255</v>
       </c>
       <c r="F92" s="2">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="G92" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H92" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B93" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C93" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="D93" s="1">
         <v>46251</v>
@@ -3548,741 +3548,741 @@
         <v>46253</v>
       </c>
       <c r="F93" s="2">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G93" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H93" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B94" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C94" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D94" s="1">
         <v>46251</v>
       </c>
       <c r="E94" s="1">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="F94" s="2">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="G94" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H94" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B95" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C95" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D95" s="1">
         <v>46251</v>
       </c>
       <c r="E95" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F95" s="2">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="G95" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H95" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B96" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C96" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D96" s="1">
         <v>46251</v>
       </c>
       <c r="E96" s="1">
-        <v>46255</v>
+        <v>46252</v>
       </c>
       <c r="F96" s="2">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="G96" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H96" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B97" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C97" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D97" s="1">
         <v>46251</v>
       </c>
       <c r="E97" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="F97" s="2">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="G97" t="s">
         <v>11</v>
       </c>
       <c r="H97" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B98" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C98" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="D98" s="1">
         <v>46251</v>
       </c>
       <c r="E98" s="1">
-        <v>46259</v>
+        <v>46253</v>
       </c>
       <c r="F98" s="2">
-        <v>8</v>
+        <v>2.1</v>
       </c>
       <c r="G98" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="H98" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B99" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C99" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D99" s="1">
         <v>46251</v>
       </c>
       <c r="E99" s="1">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="F99" s="2">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="G99" t="s">
         <v>11</v>
       </c>
       <c r="H99" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B100" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C100" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="D100" s="1">
         <v>46251</v>
       </c>
       <c r="E100" s="1">
-        <v>46261</v>
+        <v>46255</v>
       </c>
       <c r="F100" s="2">
-        <v>10.1</v>
+        <v>3.8</v>
       </c>
       <c r="G100" t="s">
         <v>11</v>
       </c>
       <c r="H100" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B101" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C101" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D101" s="1">
         <v>46251</v>
       </c>
       <c r="E101" s="1">
-        <v>46271</v>
+        <v>46256</v>
       </c>
       <c r="F101" s="2">
-        <v>19.5</v>
+        <v>4.8</v>
       </c>
       <c r="G101" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H101" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B102" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C102" t="s">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="D102" s="1">
         <v>46251</v>
       </c>
       <c r="E102" s="1">
-        <v>46258</v>
+        <v>46270</v>
       </c>
       <c r="F102" s="2">
-        <v>6.6</v>
+        <v>19.3</v>
       </c>
       <c r="G102" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H102" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B103" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C103" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="D103" s="1">
         <v>46251</v>
       </c>
       <c r="E103" s="1">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="F103" s="2">
-        <v>10.1</v>
+        <v>8.6</v>
       </c>
       <c r="G103" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H103" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B104" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C104" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D104" s="1">
         <v>46251</v>
       </c>
       <c r="E104" s="1">
-        <v>46269</v>
+        <v>46260</v>
       </c>
       <c r="F104" s="2">
-        <v>17.8</v>
+        <v>9</v>
       </c>
       <c r="G104" t="s">
         <v>11</v>
       </c>
       <c r="H104" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B105" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C105" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D105" s="1">
         <v>46251</v>
       </c>
       <c r="E105" s="1">
-        <v>46258</v>
+        <v>46263</v>
       </c>
       <c r="F105" s="2">
-        <v>6.6</v>
+        <v>12.3</v>
       </c>
       <c r="G105" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H105" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B106" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C106" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="D106" s="1">
         <v>46251</v>
       </c>
       <c r="E106" s="1">
-        <v>46256</v>
+        <v>46262</v>
       </c>
       <c r="F106" s="2">
-        <v>5.2</v>
+        <v>11.3</v>
       </c>
       <c r="G106" t="s">
         <v>11</v>
       </c>
       <c r="H106" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B107" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C107" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D107" s="1">
         <v>46251</v>
       </c>
       <c r="E107" s="1">
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="F107" s="2">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="G107" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H107" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B108" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C108" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D108" s="1">
         <v>46251</v>
       </c>
       <c r="E108" s="1">
-        <v>46253</v>
+        <v>46256</v>
       </c>
       <c r="F108" s="2">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="G108" t="s">
         <v>11</v>
       </c>
       <c r="H108" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B109" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C109" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="D109" s="1">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E109" s="1">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="F109" s="2">
-        <v>4.6</v>
+        <v>8.1</v>
       </c>
       <c r="G109" t="s">
         <v>11</v>
       </c>
       <c r="H109" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B110" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C110" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D110" s="1">
         <v>46252</v>
       </c>
       <c r="E110" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F110" s="2">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="G110" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H110" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B111" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C111" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D111" s="1">
         <v>46252</v>
       </c>
       <c r="E111" s="1">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="F111" s="2">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="G111" t="s">
         <v>11</v>
       </c>
       <c r="H111" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B112" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C112" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D112" s="1">
         <v>46252</v>
       </c>
       <c r="E112" s="1">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="F112" s="2">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="G112" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H112" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B113" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C113" t="s">
-        <v>133</v>
+        <v>66</v>
       </c>
       <c r="D113" s="1">
         <v>46252</v>
       </c>
       <c r="E113" s="1">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="F113" s="2">
-        <v>8.6</v>
+        <v>11.1</v>
       </c>
       <c r="G113" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H113" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B114" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C114" t="s">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="D114" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E114" s="1">
-        <v>46256</v>
+        <v>46261</v>
       </c>
       <c r="F114" s="2">
-        <v>3.8</v>
+        <v>7.5</v>
       </c>
       <c r="G114" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H114" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B115" t="s">
         <v>9</v>
       </c>
       <c r="C115" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D115" s="1">
         <v>46253</v>
       </c>
       <c r="E115" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F115" s="2">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="G115" t="s">
         <v>11</v>
       </c>
       <c r="H115" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B116" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C116" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D116" s="1">
         <v>46253</v>
       </c>
       <c r="E116" s="1">
-        <v>46255</v>
+        <v>46257</v>
       </c>
       <c r="F116" s="2">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="G116" t="s">
         <v>11</v>
       </c>
       <c r="H116" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B117" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C117" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="D117" s="1">
         <v>46253</v>
       </c>
       <c r="E117" s="1">
-        <v>46267</v>
+        <v>46257</v>
       </c>
       <c r="F117" s="2">
-        <v>14.3</v>
+        <v>3.7</v>
       </c>
       <c r="G117" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H117" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B118" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C118" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D118" s="1">
         <v>46253</v>
       </c>
       <c r="E118" s="1">
-        <v>46258</v>
+        <v>46256</v>
       </c>
       <c r="F118" s="2">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="G118" t="s">
         <v>11</v>
       </c>
       <c r="H118" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B119" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C119" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D119" s="1">
         <v>46253</v>
       </c>
       <c r="E119" s="1">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F119" s="2">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="G119" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H119" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B120" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C120" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D120" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="E120" s="1">
-        <v>46259</v>
+        <v>46257</v>
       </c>
       <c r="F120" s="2">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="G120" t="s">
         <v>11</v>
       </c>
       <c r="H120" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B121" t="s">
         <v>9</v>
       </c>
       <c r="C121" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D121" s="1">
         <v>46254</v>
       </c>
       <c r="E121" s="1">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="F121" s="2">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="G121" t="s">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="H121" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -4290,25 +4290,25 @@
         <v>154</v>
       </c>
       <c r="B122" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C122" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D122" s="1">
         <v>46254</v>
       </c>
       <c r="E122" s="1">
-        <v>46257</v>
+        <v>46262</v>
       </c>
       <c r="F122" s="2">
-        <v>3.1</v>
+        <v>7.8</v>
       </c>
       <c r="G122" t="s">
         <v>11</v>
       </c>
       <c r="H122" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -4316,10 +4316,10 @@
         <v>155</v>
       </c>
       <c r="B123" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C123" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D123" s="1">
         <v>46254</v>
@@ -4328,13 +4328,13 @@
         <v>46256</v>
       </c>
       <c r="F123" s="2">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="G123" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H123" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -4342,25 +4342,25 @@
         <v>156</v>
       </c>
       <c r="B124" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C124" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D124" s="1">
         <v>46254</v>
       </c>
       <c r="E124" s="1">
-        <v>46265</v>
+        <v>46256</v>
       </c>
       <c r="F124" s="2">
-        <v>10.8</v>
+        <v>2.4</v>
       </c>
       <c r="G124" t="s">
         <v>11</v>
       </c>
       <c r="H124" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -4368,25 +4368,25 @@
         <v>157</v>
       </c>
       <c r="B125" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C125" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D125" s="1">
         <v>46254</v>
       </c>
       <c r="E125" s="1">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="F125" s="2">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G125" t="s">
         <v>11</v>
       </c>
       <c r="H125" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -4394,25 +4394,25 @@
         <v>158</v>
       </c>
       <c r="B126" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C126" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D126" s="1">
         <v>46254</v>
       </c>
       <c r="E126" s="1">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="F126" s="2">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="G126" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H126" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -4420,25 +4420,25 @@
         <v>159</v>
       </c>
       <c r="B127" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C127" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D127" s="1">
         <v>46254</v>
       </c>
       <c r="E127" s="1">
-        <v>46260</v>
+        <v>46257</v>
       </c>
       <c r="F127" s="2">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="G127" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H127" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -4446,25 +4446,25 @@
         <v>160</v>
       </c>
       <c r="B128" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C128" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="D128" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="E128" s="1">
-        <v>46260</v>
+        <v>46263</v>
       </c>
       <c r="F128" s="2">
-        <v>5.2</v>
+        <v>9.1</v>
       </c>
       <c r="G128" t="s">
         <v>11</v>
       </c>
       <c r="H128" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -4472,25 +4472,25 @@
         <v>161</v>
       </c>
       <c r="B129" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C129" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D129" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="E129" s="1">
-        <v>46259</v>
+        <v>46257</v>
       </c>
       <c r="F129" s="2">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="G129" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H129" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -4501,22 +4501,22 @@
         <v>9</v>
       </c>
       <c r="C130" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D130" s="1">
         <v>46255</v>
       </c>
       <c r="E130" s="1">
-        <v>46261</v>
+        <v>46258</v>
       </c>
       <c r="F130" s="2">
-        <v>6.1</v>
+        <v>2.7</v>
       </c>
       <c r="G130" t="s">
         <v>11</v>
       </c>
       <c r="H130" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -4527,22 +4527,22 @@
         <v>9</v>
       </c>
       <c r="C131" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D131" s="1">
         <v>46255</v>
       </c>
       <c r="E131" s="1">
-        <v>46260</v>
+        <v>46257</v>
       </c>
       <c r="F131" s="2">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="G131" t="s">
         <v>11</v>
       </c>
       <c r="H131" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -4550,25 +4550,25 @@
         <v>164</v>
       </c>
       <c r="B132" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C132" t="s">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="D132" s="1">
         <v>46255</v>
       </c>
       <c r="E132" s="1">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="F132" s="2">
-        <v>5.9</v>
+        <v>12.2</v>
       </c>
       <c r="G132" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H132" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -4576,10 +4576,10 @@
         <v>165</v>
       </c>
       <c r="B133" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C133" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="D133" s="1">
         <v>46255</v>
@@ -4588,13 +4588,13 @@
         <v>46262</v>
       </c>
       <c r="F133" s="2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="G133" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H133" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -4602,25 +4602,25 @@
         <v>166</v>
       </c>
       <c r="B134" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C134" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D134" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="E134" s="1">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="F134" s="2">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="G134" t="s">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="H134" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -4628,25 +4628,25 @@
         <v>167</v>
       </c>
       <c r="B135" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C135" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="D135" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="E135" s="1">
-        <v>46257</v>
+        <v>46265</v>
       </c>
       <c r="F135" s="2">
-        <v>2.2</v>
+        <v>7</v>
       </c>
       <c r="G135" t="s">
         <v>11</v>
       </c>
       <c r="H135" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -4657,7 +4657,7 @@
         <v>9</v>
       </c>
       <c r="C136" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D136" s="1">
         <v>46258</v>
@@ -4672,7 +4672,7 @@
         <v>11</v>
       </c>
       <c r="H136" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -4683,22 +4683,22 @@
         <v>9</v>
       </c>
       <c r="C137" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D137" s="1">
         <v>46258</v>
       </c>
       <c r="E137" s="1">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="F137" s="2">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="G137" t="s">
         <v>11</v>
       </c>
       <c r="H137" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -4709,22 +4709,22 @@
         <v>9</v>
       </c>
       <c r="C138" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D138" s="1">
         <v>46258</v>
       </c>
       <c r="E138" s="1">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="F138" s="2">
-        <v>7.3</v>
+        <v>5.7</v>
       </c>
       <c r="G138" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H138" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -4732,25 +4732,25 @@
         <v>171</v>
       </c>
       <c r="B139" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C139" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D139" s="1">
         <v>46258</v>
       </c>
       <c r="E139" s="1">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="F139" s="2">
-        <v>7.3</v>
+        <v>2</v>
       </c>
       <c r="G139" t="s">
         <v>11</v>
       </c>
       <c r="H139" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -4758,25 +4758,25 @@
         <v>172</v>
       </c>
       <c r="B140" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C140" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="D140" s="1">
         <v>46258</v>
       </c>
       <c r="E140" s="1">
-        <v>46263</v>
+        <v>46260</v>
       </c>
       <c r="F140" s="2">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="G140" t="s">
         <v>11</v>
       </c>
       <c r="H140" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -4784,25 +4784,25 @@
         <v>173</v>
       </c>
       <c r="B141" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C141" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="D141" s="1">
         <v>46258</v>
       </c>
       <c r="E141" s="1">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="F141" s="2">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="G141" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H141" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -4810,10 +4810,10 @@
         <v>174</v>
       </c>
       <c r="B142" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C142" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="D142" s="1">
         <v>46258</v>
@@ -4822,13 +4822,13 @@
         <v>46262</v>
       </c>
       <c r="F142" s="2">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="G142" t="s">
         <v>11</v>
       </c>
       <c r="H142" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -4836,25 +4836,25 @@
         <v>175</v>
       </c>
       <c r="B143" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C143" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="D143" s="1">
         <v>46258</v>
       </c>
       <c r="E143" s="1">
-        <v>46261</v>
+        <v>46269</v>
       </c>
       <c r="F143" s="2">
-        <v>2.6</v>
+        <v>10.8</v>
       </c>
       <c r="G143" t="s">
         <v>11</v>
       </c>
       <c r="H143" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -4862,25 +4862,25 @@
         <v>176</v>
       </c>
       <c r="B144" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C144" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="D144" s="1">
         <v>46258</v>
       </c>
       <c r="E144" s="1">
-        <v>46261</v>
+        <v>46271</v>
       </c>
       <c r="F144" s="2">
-        <v>3.3</v>
+        <v>12.8</v>
       </c>
       <c r="G144" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H144" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -4888,25 +4888,25 @@
         <v>177</v>
       </c>
       <c r="B145" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C145" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="D145" s="1">
         <v>46258</v>
       </c>
       <c r="E145" s="1">
-        <v>46261</v>
+        <v>46275</v>
       </c>
       <c r="F145" s="2">
-        <v>2.6</v>
+        <v>16.6</v>
       </c>
       <c r="G145" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H145" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -4914,25 +4914,25 @@
         <v>178</v>
       </c>
       <c r="B146" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C146" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D146" s="1">
         <v>46258</v>
       </c>
       <c r="E146" s="1">
-        <v>46266</v>
+        <v>46275</v>
       </c>
       <c r="F146" s="2">
-        <v>8.3</v>
+        <v>17.1</v>
       </c>
       <c r="G146" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H146" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -4940,25 +4940,25 @@
         <v>179</v>
       </c>
       <c r="B147" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C147" t="s">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="D147" s="1">
         <v>46258</v>
       </c>
       <c r="E147" s="1">
-        <v>46269</v>
+        <v>46263</v>
       </c>
       <c r="F147" s="2">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="G147" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H147" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -4966,7 +4966,7 @@
         <v>180</v>
       </c>
       <c r="B148" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C148" t="s">
         <v>36</v>
@@ -4975,16 +4975,16 @@
         <v>46258</v>
       </c>
       <c r="E148" s="1">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="F148" s="2">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="G148" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H148" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -4992,25 +4992,25 @@
         <v>181</v>
       </c>
       <c r="B149" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C149" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D149" s="1">
         <v>46258</v>
       </c>
       <c r="E149" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="F149" s="2">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="G149" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H149" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -5021,22 +5021,22 @@
         <v>9</v>
       </c>
       <c r="C150" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D150" s="1">
         <v>46259</v>
       </c>
       <c r="E150" s="1">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="F150" s="2">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="G150" t="s">
         <v>11</v>
       </c>
       <c r="H150" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -5044,22 +5044,22 @@
         <v>183</v>
       </c>
       <c r="B151" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C151" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D151" s="1">
         <v>46259</v>
       </c>
       <c r="E151" s="1">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="F151" s="2">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="G151" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H151" t="s">
         <v>12</v>
@@ -5070,10 +5070,10 @@
         <v>184</v>
       </c>
       <c r="B152" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C152" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D152" s="1">
         <v>46259</v>
@@ -5082,13 +5082,13 @@
         <v>46263</v>
       </c>
       <c r="F152" s="2">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="G152" t="s">
         <v>11</v>
       </c>
       <c r="H152" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -5096,25 +5096,25 @@
         <v>185</v>
       </c>
       <c r="B153" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C153" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="D153" s="1">
         <v>46259</v>
       </c>
       <c r="E153" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="F153" s="2">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="G153" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H153" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -5122,25 +5122,25 @@
         <v>186</v>
       </c>
       <c r="B154" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C154" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D154" s="1">
         <v>46259</v>
       </c>
       <c r="E154" s="1">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="F154" s="2">
-        <v>1.8</v>
+        <v>8.3</v>
       </c>
       <c r="G154" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H154" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -5148,25 +5148,25 @@
         <v>187</v>
       </c>
       <c r="B155" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C155" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D155" s="1">
         <v>46259</v>
       </c>
       <c r="E155" s="1">
-        <v>46270</v>
+        <v>46264</v>
       </c>
       <c r="F155" s="2">
-        <v>10.8</v>
+        <v>5.2</v>
       </c>
       <c r="G155" t="s">
         <v>11</v>
       </c>
       <c r="H155" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
@@ -5174,25 +5174,25 @@
         <v>188</v>
       </c>
       <c r="B156" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C156" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="D156" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E156" s="1">
-        <v>46271</v>
+        <v>46262</v>
       </c>
       <c r="F156" s="2">
-        <v>11.6</v>
+        <v>2.1</v>
       </c>
       <c r="G156" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H156" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
@@ -5203,22 +5203,22 @@
         <v>9</v>
       </c>
       <c r="C157" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D157" s="1">
         <v>46260</v>
       </c>
       <c r="E157" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F157" s="2">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
       <c r="G157" t="s">
         <v>11</v>
       </c>
       <c r="H157" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -5226,25 +5226,25 @@
         <v>190</v>
       </c>
       <c r="B158" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C158" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D158" s="1">
         <v>46260</v>
       </c>
       <c r="E158" s="1">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="F158" s="2">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="G158" t="s">
         <v>11</v>
       </c>
       <c r="H158" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -5252,10 +5252,10 @@
         <v>191</v>
       </c>
       <c r="B159" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C159" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D159" s="1">
         <v>46260</v>
@@ -5264,13 +5264,13 @@
         <v>46262</v>
       </c>
       <c r="F159" s="2">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="G159" t="s">
         <v>11</v>
       </c>
       <c r="H159" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -5278,25 +5278,25 @@
         <v>192</v>
       </c>
       <c r="B160" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C160" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D160" s="1">
         <v>46260</v>
       </c>
       <c r="E160" s="1">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="F160" s="2">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="G160" t="s">
         <v>11</v>
       </c>
       <c r="H160" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -5304,25 +5304,25 @@
         <v>193</v>
       </c>
       <c r="B161" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C161" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D161" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E161" s="1">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="F161" s="2">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="G161" t="s">
         <v>11</v>
       </c>
       <c r="H161" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
@@ -5330,25 +5330,25 @@
         <v>194</v>
       </c>
       <c r="B162" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C162" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D162" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E162" s="1">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="F162" s="2">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="G162" t="s">
         <v>11</v>
       </c>
       <c r="H162" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -5356,25 +5356,25 @@
         <v>195</v>
       </c>
       <c r="B163" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C163" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="D163" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E163" s="1">
-        <v>46276</v>
+        <v>46267</v>
       </c>
       <c r="F163" s="2">
-        <v>15.7</v>
+        <v>6</v>
       </c>
       <c r="G163" t="s">
         <v>11</v>
       </c>
       <c r="H163" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -5382,25 +5382,25 @@
         <v>196</v>
       </c>
       <c r="B164" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C164" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D164" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E164" s="1">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="F164" s="2">
-        <v>4.6</v>
+        <v>7.7</v>
       </c>
       <c r="G164" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H164" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -5408,25 +5408,25 @@
         <v>197</v>
       </c>
       <c r="B165" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C165" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="D165" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E165" s="1">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="F165" s="2">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="G165" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H165" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -5437,22 +5437,22 @@
         <v>9</v>
       </c>
       <c r="C166" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D166" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E166" s="1">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="F166" s="2">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="G166" t="s">
         <v>11</v>
       </c>
       <c r="H166" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
@@ -5463,22 +5463,22 @@
         <v>9</v>
       </c>
       <c r="C167" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="D167" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E167" s="1">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="F167" s="2">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="G167" t="s">
         <v>11</v>
       </c>
       <c r="H167" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -5486,16 +5486,16 @@
         <v>200</v>
       </c>
       <c r="B168" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C168" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D168" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E168" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F168" s="2">
         <v>4</v>
@@ -5504,7 +5504,7 @@
         <v>11</v>
       </c>
       <c r="H168" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -5512,25 +5512,25 @@
         <v>201</v>
       </c>
       <c r="B169" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C169" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D169" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E169" s="1">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="F169" s="2">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="G169" t="s">
         <v>11</v>
       </c>
       <c r="H169" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
@@ -5538,19 +5538,19 @@
         <v>202</v>
       </c>
       <c r="B170" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C170" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D170" s="1">
         <v>46262</v>
       </c>
       <c r="E170" s="1">
-        <v>46270</v>
+        <v>46265</v>
       </c>
       <c r="F170" s="2">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="G170" t="s">
         <v>11</v>
@@ -5564,25 +5564,25 @@
         <v>203</v>
       </c>
       <c r="B171" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C171" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D171" s="1">
         <v>46262</v>
       </c>
       <c r="E171" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F171" s="2">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="G171" t="s">
         <v>11</v>
       </c>
       <c r="H171" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -5590,25 +5590,25 @@
         <v>204</v>
       </c>
       <c r="B172" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C172" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D172" s="1">
         <v>46262</v>
       </c>
       <c r="E172" s="1">
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="F172" s="2">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="G172" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H172" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -5616,25 +5616,25 @@
         <v>205</v>
       </c>
       <c r="B173" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C173" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D173" s="1">
         <v>46262</v>
       </c>
       <c r="E173" s="1">
-        <v>46265</v>
+        <v>46282</v>
       </c>
       <c r="F173" s="2">
-        <v>3.4</v>
+        <v>20.3</v>
       </c>
       <c r="G173" t="s">
         <v>11</v>
       </c>
       <c r="H173" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -5642,25 +5642,25 @@
         <v>206</v>
       </c>
       <c r="B174" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C174" t="s">
-        <v>133</v>
+        <v>10</v>
       </c>
       <c r="D174" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="E174" s="1">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="F174" s="2">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="G174" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H174" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
@@ -5668,25 +5668,25 @@
         <v>207</v>
       </c>
       <c r="B175" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C175" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D175" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="E175" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F175" s="2">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="G175" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H175" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
@@ -5694,25 +5694,25 @@
         <v>208</v>
       </c>
       <c r="B176" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C176" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D176" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="E176" s="1">
-        <v>46266</v>
+        <v>46272</v>
       </c>
       <c r="F176" s="2">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="G176" t="s">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="H176" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
@@ -5723,22 +5723,22 @@
         <v>9</v>
       </c>
       <c r="C177" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D177" s="1">
         <v>46265</v>
       </c>
       <c r="E177" s="1">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="F177" s="2">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="G177" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H177" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
@@ -5749,22 +5749,22 @@
         <v>9</v>
       </c>
       <c r="C178" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D178" s="1">
         <v>46265</v>
       </c>
       <c r="E178" s="1">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="F178" s="2">
-        <v>4.4</v>
+        <v>7.1</v>
       </c>
       <c r="G178" t="s">
         <v>11</v>
       </c>
       <c r="H178" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -5781,16 +5781,16 @@
         <v>46265</v>
       </c>
       <c r="E179" s="1">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="F179" s="2">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="G179" t="s">
         <v>11</v>
       </c>
       <c r="H179" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
@@ -5801,22 +5801,22 @@
         <v>9</v>
       </c>
       <c r="C180" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D180" s="1">
         <v>46265</v>
       </c>
       <c r="E180" s="1">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="F180" s="2">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="G180" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H180" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
@@ -5827,22 +5827,22 @@
         <v>9</v>
       </c>
       <c r="C181" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D181" s="1">
         <v>46265</v>
       </c>
       <c r="E181" s="1">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="F181" s="2">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="G181" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H181" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -5850,19 +5850,19 @@
         <v>214</v>
       </c>
       <c r="B182" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C182" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D182" s="1">
         <v>46265</v>
       </c>
       <c r="E182" s="1">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="F182" s="2">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="G182" t="s">
         <v>11</v>
@@ -5876,25 +5876,25 @@
         <v>215</v>
       </c>
       <c r="B183" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C183" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D183" s="1">
         <v>46265</v>
       </c>
       <c r="E183" s="1">
-        <v>46270</v>
+        <v>46268</v>
       </c>
       <c r="F183" s="2">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="G183" t="s">
         <v>11</v>
       </c>
       <c r="H183" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -5902,25 +5902,25 @@
         <v>216</v>
       </c>
       <c r="B184" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C184" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D184" s="1">
         <v>46265</v>
       </c>
       <c r="E184" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F184" s="2">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="G184" t="s">
         <v>11</v>
       </c>
       <c r="H184" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -5928,25 +5928,25 @@
         <v>217</v>
       </c>
       <c r="B185" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C185" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D185" s="1">
         <v>46265</v>
       </c>
       <c r="E185" s="1">
-        <v>46267</v>
+        <v>46271</v>
       </c>
       <c r="F185" s="2">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="G185" t="s">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="H185" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -5954,25 +5954,25 @@
         <v>218</v>
       </c>
       <c r="B186" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C186" t="s">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="D186" s="1">
         <v>46265</v>
       </c>
       <c r="E186" s="1">
-        <v>46277</v>
+        <v>46269</v>
       </c>
       <c r="F186" s="2">
-        <v>12.4</v>
+        <v>3.6</v>
       </c>
       <c r="G186" t="s">
         <v>11</v>
       </c>
       <c r="H186" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -5980,25 +5980,25 @@
         <v>219</v>
       </c>
       <c r="B187" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C187" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="D187" s="1">
         <v>46265</v>
       </c>
       <c r="E187" s="1">
-        <v>46277</v>
+        <v>46268</v>
       </c>
       <c r="F187" s="2">
-        <v>11.6</v>
+        <v>2.8</v>
       </c>
       <c r="G187" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H187" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -6006,25 +6006,25 @@
         <v>220</v>
       </c>
       <c r="B188" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C188" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="D188" s="1">
         <v>46265</v>
       </c>
       <c r="E188" s="1">
-        <v>46271</v>
+        <v>46269</v>
       </c>
       <c r="F188" s="2">
-        <v>5.7</v>
+        <v>3.9</v>
       </c>
       <c r="G188" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H188" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
@@ -6032,25 +6032,25 @@
         <v>221</v>
       </c>
       <c r="B189" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C189" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D189" s="1">
         <v>46265</v>
       </c>
       <c r="E189" s="1">
-        <v>46268</v>
+        <v>46279</v>
       </c>
       <c r="F189" s="2">
-        <v>2.5</v>
+        <v>14.4</v>
       </c>
       <c r="G189" t="s">
         <v>11</v>
       </c>
       <c r="H189" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
@@ -6058,10 +6058,10 @@
         <v>222</v>
       </c>
       <c r="B190" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C190" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D190" s="1">
         <v>46265</v>
@@ -6070,13 +6070,13 @@
         <v>46270</v>
       </c>
       <c r="F190" s="2">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="G190" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H190" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
@@ -6084,25 +6084,25 @@
         <v>223</v>
       </c>
       <c r="B191" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C191" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D191" s="1">
         <v>46265</v>
       </c>
       <c r="E191" s="1">
-        <v>46268</v>
+        <v>46271</v>
       </c>
       <c r="F191" s="2">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="G191" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H191" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
